--- a/assets/files/templates/SafePlum_ppe_ledger.xlsx
+++ b/assets/files/templates/SafePlum_ppe_ledger.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="84">
   <si>
     <r>
       <rPr>
@@ -716,9 +716,6 @@
     <t xml:space="preserve">수령 서명</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-27</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -795,9 +792,6 @@
     <t xml:space="preserve">신규 입사</t>
   </si>
   <si>
-    <t xml:space="preserve">2027-10-26</t>
-  </si>
-  <si>
     <t xml:space="preserve">지급 건수</t>
   </si>
   <si>
@@ -978,9 +972,6 @@
       </rPr>
       <t xml:space="preserve">개</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-27</t>
   </si>
   <si>
     <t xml:space="preserve">작업별 보호구 지급 기준</t>
@@ -2600,29 +2591,29 @@
       <c r="A6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="14" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="D6" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="E6" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="F6" s="16" t="s">
         <v>28</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>29</v>
       </c>
       <c r="G6" s="16" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>46686</v>
       </c>
       <c r="J6" s="17" t="str">
         <f aca="true">IF(I6="","",IF(I6&lt;TODAY(),"교체 필요",IF(I6-TODAY()&lt;=30,"30일 이내","사용 중")))</f>
@@ -3226,28 +3217,28 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C41" s="19" t="n">
         <f aca="false">COUNTA(E6:E39)</f>
         <v>1</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E41" s="19" t="n">
         <f aca="false">SUM(G6:G39)</f>
         <v>1</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G41" s="20" t="n">
         <f aca="false">COUNTIF(J6:J39,"교체 필요")</f>
         <v>0</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I41" s="19" t="n">
         <f aca="false">COUNTIF(J6:J39,"30일 이내")</f>
@@ -3313,7 +3304,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3323,7 +3314,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -3336,51 +3327,51 @@
         <v>14</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>41</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>25</v>
+      <c r="B5" s="14" t="n">
+        <v>46322</v>
       </c>
       <c r="C5" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="F5" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="G5" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>49</v>
+      <c r="H5" s="14" t="n">
+        <v>46353</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3782,153 +3773,153 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>

--- a/assets/files/templates/SafePlum_ppe_ledger.xlsx
+++ b/assets/files/templates/SafePlum_ppe_ledger.xlsx
@@ -2445,17 +2445,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
